--- a/verified_data.xlsx
+++ b/verified_data.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82880</v>
+        <v>87331</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47685</v>
+        <v>87331</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22761</v>
+        <v>87331</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>88693</v>
+        <v>87331</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>

--- a/verified_data.xlsx
+++ b/verified_data.xlsx
@@ -413,113 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>voucher_date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entry No</t>
+          <t>entry_no</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Voucher Type</t>
+          <t>sub_account</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Sub Account</t>
+          <t>details</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>debit_amount</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Narration</t>
+          <t>credit_amount</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Debit Amount</t>
+          <t>account_code</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Credit Amount</t>
+          <t>country</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>region</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Reference Number</t>
+          <t>class</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Party Name</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>GST Number</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cost Center</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Account Code</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Invoice Number</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Sub Class</t>
+          <t>sub_class</t>
         </is>
       </c>
     </row>
@@ -534,7 +484,11 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cost of Sales</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
@@ -542,45 +496,31 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>884.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>884.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Trading account</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
         </is>
@@ -597,53 +537,43 @@
           <t>1.2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
           <t>Cost of Sales</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>884.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>884.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
@@ -660,7 +590,11 @@
           <t>2.1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cost of Sales</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
@@ -668,45 +602,31 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>1120.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1120.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Trading account</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
         </is>
@@ -723,53 +643,43 @@
           <t>2.2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>Cost of Sales</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1120.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1120.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
@@ -786,53 +696,43 @@
           <t>3.1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Advertisements</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Credit Expenses</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Credit Expenses</t>
+          <t>2394.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2394.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Operating account</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Operating Expenses</t>
         </is>
@@ -849,53 +749,43 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Accrued Expenses</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Accrued Expenses</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
           <t>Credit Expenses</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2394.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2394.0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Liabilities and Owners Equity</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
@@ -912,53 +802,43 @@
           <t>4.1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>Credit Sales</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2948.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2948.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Trading account</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
@@ -975,53 +855,43 @@
           <t>4.2</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Trade Receivables</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Trade Receivables</t>
+          <t>Credit Sales</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Credit Sales</t>
+          <t>2940.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2940.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
@@ -1038,53 +908,43 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>Cash Sales</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3734.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3734.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Trading account</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
@@ -1101,53 +961,43 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cash at Bank</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Cash Sales</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cash Sales</t>
+          <t>3723.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3723.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
@@ -1164,7 +1014,11 @@
           <t>6.1</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cost of Sales</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
@@ -1172,45 +1026,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>4371.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4371.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Trading account</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
         </is>
@@ -1227,53 +1067,43 @@
           <t>6.2</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
           <t>Cost of Sales</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4371.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4371.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
@@ -1290,53 +1120,43 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
           <t>Credit Sales</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>14570.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14570.0</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Trading account</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
@@ -1353,53 +1173,43 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trade Receivables</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Trade Receivables</t>
+          <t>Credit Sales</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Credit Sales</t>
+          <t>14570.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14570.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>

--- a/verified_data.xlsx
+++ b/verified_data.xlsx
@@ -476,245 +476,205 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cost of Sales</t>
-        </is>
-      </c>
+          <t>2001.1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Cash Sale Debit</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>884.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Trading account</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Cost of Sales</t>
-        </is>
-      </c>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
+          <t>2001.2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Cash Sale Credit</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>884.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2002.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Service Revenue Debit</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1120.0</t>
+          <t>7200.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Trading account</t>
+          <t>Operating account</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
+          <t>2002.2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1120.0</t>
-        </is>
-      </c>
+          <t>Service Revenue Credit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Advertisements</t>
-        </is>
-      </c>
+          <t>2003.1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Credit Expenses</t>
+          <t>Inventory Purchase Debit</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2394.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>854</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,47 +687,35 @@
           <t>North America</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Operating account</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Accrued Expenses</t>
-        </is>
-      </c>
+          <t>2003.2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Credit Expenses</t>
+          <t>Inventory Purchase Credit</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2394.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -780,259 +728,199 @@
           <t>North America</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Liabilities and Owners Equity</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+          <t>2004.1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Credit Sales</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2948.0</t>
-        </is>
-      </c>
+          <t>Office Rent Debit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>658</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Trading account</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Trade Receivables</t>
-        </is>
-      </c>
+          <t>2004.2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Credit Sales</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2940.0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Office Rent Credit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2700.0</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+          <t>2005.1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cash Sales</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3734.0</t>
-        </is>
-      </c>
+          <t>Equipment Purchase Debit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>15000.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Trading account</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Cash at Bank</t>
-        </is>
-      </c>
+          <t>2005.2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cash Sales</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3723.0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>Equipment Purchase Credit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15000.0</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>132</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Cost of Sales</t>
-        </is>
-      </c>
+          <t>2006.1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Salary Expense Debit</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4371.0</t>
+          <t>8500.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>195</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1045,47 +933,35 @@
           <t>North America</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Trading account</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Cost of Sales</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
+          <t>2006.2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Salary Expense Credit</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4371.0</t>
+          <t>8500.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1098,47 +974,35 @@
           <t>North America</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+          <t>2007.1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Credit Sales</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>14570.0</t>
-        </is>
-      </c>
+          <t>Insurance Payment Debit</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4000.0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>716</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1151,47 +1015,35 @@
           <t>North America</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Trading account</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2018-01-01 00:00:00</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Trade Receivables</t>
-        </is>
-      </c>
+          <t>2007.2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Credit Sales</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>14570.0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>Insurance Payment Credit</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3700.0</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1204,16 +1056,8 @@
           <t>North America</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
